--- a/location-filters.xlsx
+++ b/location-filters.xlsx
@@ -1523,7 +1523,7 @@
     </row>
     <row r="2">
       <c r="C2" s="2" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
     </row>
   </sheetData>
